--- a/hasil_analisis_mitra_distinct.xlsx
+++ b/hasil_analisis_mitra_distinct.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\repos\kerjasama\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{99E45FAD-0A6D-4860-A217-1C1296B0395A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2CC2FC45-D313-4BAB-9144-8971DCC44AD1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="29355" yWindow="300" windowWidth="27600" windowHeight="15165" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3410,9 +3410,185 @@
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{6C5F493D-E88B-4580-8446-00CCD27D6EE3}" name="Table1" displayName="Table1" ref="A1:L220" totalsRowShown="0">
   <autoFilter ref="A1:L220" xr:uid="{6C5F493D-E88B-4580-8446-00CCD27D6EE3}">
-    <filterColumn colId="11">
-      <filters>
-        <filter val="Semester 2023/2024"/>
+    <filterColumn colId="9">
+      <filters blank="1">
+        <filter val="0147/PL16/KS/2024"/>
+        <filter val="0204/PL16/KS.00.01/2025"/>
+        <filter val="0382/PL16/KS.11/2025"/>
+        <filter val="0756/PL16/KS.00.00/2025"/>
+        <filter val="0826/PL16/KS/2024"/>
+        <filter val="0983/PL16/KS/2024"/>
+        <filter val="10063/PL16/KS.00.00/2024"/>
+        <filter val="10234/PL16/KS.00.00/2024"/>
+        <filter val="10381/PL16/KS.00.00/2024"/>
+        <filter val="1039/PL16/KS.00.00/2025"/>
+        <filter val="10402/PL16/KS.00.00/2024"/>
+        <filter val="10696/PL16/KS.00.01/2024"/>
+        <filter val="10886/PL16/KS.00.00/2025"/>
+        <filter val="10908/PL16/KS/2024"/>
+        <filter val="10961/PL16/KS.00.00/2024"/>
+        <filter val="11075/PL16/KS.00.00/2024"/>
+        <filter val="11134/PL16/KS.00.00/2024"/>
+        <filter val="11257/PL16/KS.00.00/2024"/>
+        <filter val="11473/PL16/KS.00.00/2024"/>
+        <filter val="11825/PL16/KS.00.00/2024"/>
+        <filter val="12185/PL16/KS.00.00/2024"/>
+        <filter val="12205/PL16/KS.00.00/2024"/>
+        <filter val="12206/PL16/KS.00.00/2024"/>
+        <filter val="12207/PL16/KS.00.00/2024"/>
+        <filter val="12208/PL16/KS.00/2024"/>
+        <filter val="12471/PL16/KS.00.00/2024"/>
+        <filter val="12491/PL16/KS.00.00/2025"/>
+        <filter val="12702/ PL16/KS.00.00/2025"/>
+        <filter val="12704/PL16/KS.00.00/2025"/>
+        <filter val="13049/PL16/KS.00.00/2025"/>
+        <filter val="13675/PL16/KS.00.00/2025"/>
+        <filter val="13728/PL16/KS.00.00/2025"/>
+        <filter val="14059/PL16/KS.00.00/2024"/>
+        <filter val="14426/PL16/DT.06.01/2024"/>
+        <filter val="14812/PL16/KS.00.00/2025"/>
+        <filter val="15295/PL16/KS.00.00/2025"/>
+        <filter val="15476/PL16/KS.00.00/2025"/>
+        <filter val="15529/PL16/KS.00.00/2025"/>
+        <filter val="1553/PL16/KS/2024"/>
+        <filter val="15538/PL16/KS.00.00/2025"/>
+        <filter val="2115/PL16/KS/2024"/>
+        <filter val="2264/PL16/KS/2024"/>
+        <filter val="2314/PL16/KS/2024"/>
+        <filter val="2546/PL16/KS/2024"/>
+        <filter val="2703/PL16/KS/2024"/>
+        <filter val="3034/PL16/KS.00.00/2025"/>
+        <filter val="3079/PL16/KS/2024"/>
+        <filter val="3130/PL16/DT.06.01/2024"/>
+        <filter val="3340/PL16/KS/2024"/>
+        <filter val="3356/PL16/KS/2024"/>
+        <filter val="3502/PL16/KS.00.00/2025"/>
+        <filter val="3503/PL16/KS.00.00/2025"/>
+        <filter val="356/PL16/KS.BIV/2023"/>
+        <filter val="370/PL16/KS.BIV/2023"/>
+        <filter val="3794/PL16/KS.00.00/2025"/>
+        <filter val="397/PL16/KS.BIV/2023"/>
+        <filter val="4065/PL16/KS.BIV/2023"/>
+        <filter val="4172/PL16/KS.00.00/2025"/>
+        <filter val="420/PL16/KS.BIV/2023"/>
+        <filter val="421/PL16/KS.BIV/2023"/>
+        <filter val="423/PL16/KS.BIV/2023"/>
+        <filter val="425/PL16/KS.BIV/2023"/>
+        <filter val="4504/PL16/KS/2024"/>
+        <filter val="4510/PL16/KS.00.00/2025"/>
+        <filter val="455/PL16/KS.BIV/2023"/>
+        <filter val="455/PL16/KS.BIV/2023 (ver.2)"/>
+        <filter val="4721/PL16/KS.00.00/2025"/>
+        <filter val="473/PL16/KS.BIV/2023"/>
+        <filter val="4852/PL16/KS/2024"/>
+        <filter val="4933/PL16/KS/2024"/>
+        <filter val="4934/PL16/KS/2024"/>
+        <filter val="498/PL16/KS.BIV/2023"/>
+        <filter val="5005/PL16/KS/2024"/>
+        <filter val="503/PL16/KS.BIV/2023"/>
+        <filter val="504/PL16/KS.BIV/2023"/>
+        <filter val="505/PL16/KS.BIV/2023"/>
+        <filter val="5116/PL16/KS.00.00/2025"/>
+        <filter val="5274/PL16/KS/2024"/>
+        <filter val="5304/PL16/KS/2023"/>
+        <filter val="5326/PL16/KS/2024"/>
+        <filter val="5338/PL16/KS/2024"/>
+        <filter val="5339/PL16/KS/2024"/>
+        <filter val="5352/PL16/KS/2023"/>
+        <filter val="5444/PL16/KS.00.00/2025"/>
+        <filter val="5480/PL16/KS.00.00/2025"/>
+        <filter val="5536/PL16/KS/2024"/>
+        <filter val="5551/PL16/KS.00.00/2025"/>
+        <filter val="5554/PL16/KS.00.00/2025"/>
+        <filter val="565/PL16/KS.BIV/2023"/>
+        <filter val="5719/PL16/KS/2024"/>
+        <filter val="5751/PL16/KS/2024"/>
+        <filter val="580/PL16/KS.BIV/2023"/>
+        <filter val="581/PL16/KS.BIV/2023"/>
+        <filter val="582/PL16/KS.BIV/2023"/>
+        <filter val="583/PL16/KS.BIV/2023"/>
+        <filter val="5834/Pl16/KS/2024"/>
+        <filter val="5837/PL16/KS/2024"/>
+        <filter val="584/PL16/KS.BIV/2023"/>
+        <filter val="586/PL16/KS.BIV/2023"/>
+        <filter val="5865/PL16/KS.00.00/2025"/>
+        <filter val="587/PL16/KS.BIV/2023"/>
+        <filter val="588/PL16/KS.BIV/2023"/>
+        <filter val="589/001/SON-PON/X/2023"/>
+        <filter val="590/PL16/KS.BIV/2023"/>
+        <filter val="592/PL16/KS.BIV/2023"/>
+        <filter val="593/PL16/KS.BIV/2023"/>
+        <filter val="594/PL16/KS.BIV/2023"/>
+        <filter val="595/PL16/KS.BIV/2023"/>
+        <filter val="5962/PL16/KS/2024"/>
+        <filter val="597/PL16/KS.BIV/2023"/>
+        <filter val="6001/PL16/KS/2024"/>
+        <filter val="6014/PL16/KS/2024"/>
+        <filter val="6015/PL16/KS/2024"/>
+        <filter val="6016/PL16/KS/2024"/>
+        <filter val="6017/PL16/KS/2024"/>
+        <filter val="6018/PL16/KS/2024"/>
+        <filter val="6019/PL16/KS/2024"/>
+        <filter val="6020/PL16/KS/2024"/>
+        <filter val="6021/PL16/KS/2024"/>
+        <filter val="6022/PL16/KS/2024"/>
+        <filter val="6060/PL16/KS.00.00/2025"/>
+        <filter val="6104/PL16/KS.00.00/2025"/>
+        <filter val="617/PL16/KS.BIV/2023"/>
+        <filter val="619/PL16/KS.BIV/2023"/>
+        <filter val="6389/PL16/KS/2024"/>
+        <filter val="646/PL16/KS.BIV/2023"/>
+        <filter val="648/PL16/KS.BIV/2023"/>
+        <filter val="649/PL16/KS.BIV/2023"/>
+        <filter val="6656/PL16/KS.00.00/2025"/>
+        <filter val="6659/PL16/KS.00.00/2025"/>
+        <filter val="6819/PL16/KS.00.00/2025"/>
+        <filter val="6841/PL16/KS.00.00/2025"/>
+        <filter val="6878/PL16/KS.00.00/2025"/>
+        <filter val="6884/PL16/KS.00.00/2025"/>
+        <filter val="6885/PL16/KS.00.00/2025"/>
+        <filter val="6902/PL16/KS/2024"/>
+        <filter val="692/PL16/KS.BIV/2023"/>
+        <filter val="6924/PL16/KS.00.00/2025"/>
+        <filter val="695/PL16/KS.BIV/2023 (Ver.2)"/>
+        <filter val="6986/PL16/KS/2024"/>
+        <filter val="7004/PL16/KS/2024"/>
+        <filter val="7005/PL16/DT.06.00/2024"/>
+        <filter val="7036/PL16/KS.00.00/2025"/>
+        <filter val="7083/PL16/KS.00.00/2025"/>
+        <filter val="7084/PL16/KS.00.00/2025"/>
+        <filter val="7152/PL16/KS.00.00/2025"/>
+        <filter val="7178/PL16/KS.00.00/2025"/>
+        <filter val="7303/PL16/KS.00.00/2025"/>
+        <filter val="7335/PL16/KS.00.00/2025"/>
+        <filter val="7341/PL16/KS.00.00/2025"/>
+        <filter val="7355/PL16/KS.00.00/2025"/>
+        <filter val="7554/PL16/KS.00.00/2025"/>
+        <filter val="7697/PL16/KS.00.00/2025"/>
+        <filter val="7737/PL16/KS.00.00/2025"/>
+        <filter val="7779/PL16/KS.00.00/2025"/>
+        <filter val="7815/PL16/KS.00.00/2025"/>
+        <filter val="7859/PL16/KS.00.00/2025"/>
+        <filter val="8034/Pl16/KS/2024"/>
+        <filter val="8251/PL16/KS/2024"/>
+        <filter val="8261/PL16/KS.00.00/2024"/>
+        <filter val="8262/PL16/KS.00.00/2024"/>
+        <filter val="8279/PL16/KS/2024"/>
+        <filter val="8280/PL16/KS/2024"/>
+        <filter val="8308/PL16/KS/2024"/>
+        <filter val="8309/PL16/KS/2024"/>
+        <filter val="8360/PL16/KS/2024"/>
+        <filter val="8458/PL16/KS/2024"/>
+        <filter val="8615/PL16/KS.00.00/2024"/>
+        <filter val="8787/PL16/KS/2024"/>
+        <filter val="8836/PL16/KS/2024"/>
+        <filter val="8883/PL16/KS/2024"/>
+        <filter val="9024/Pl16/KS/2024"/>
+        <filter val="9203/PL16/KS/2024"/>
+        <filter val="9222/PL16/KS.00.00/2025"/>
+        <filter val="9316/PL16/KS.00.00/2024"/>
+        <filter val="9484/PL16/KS.00.00/2025"/>
+        <filter val="9885/PL16/KS.00.00/2025"/>
       </filters>
     </filterColumn>
   </autoFilter>
@@ -3776,7 +3952,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>1</v>
       </c>
@@ -3796,7 +3972,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>2</v>
       </c>
@@ -3816,7 +3992,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>3</v>
       </c>
@@ -3836,7 +4012,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>4</v>
       </c>
@@ -3856,7 +4032,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>5</v>
       </c>
@@ -4904,7 +5080,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="50" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A50">
         <v>49</v>
       </c>
@@ -4924,7 +5100,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="51" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A51">
         <v>50</v>
       </c>
@@ -4944,7 +5120,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="52" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A52">
         <v>51</v>
       </c>
@@ -4964,7 +5140,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="53" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A53">
         <v>52</v>
       </c>
@@ -4984,7 +5160,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="54" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A54">
         <v>53</v>
       </c>
@@ -5004,7 +5180,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="55" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A55">
         <v>54</v>
       </c>
@@ -5024,7 +5200,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="56" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A56">
         <v>55</v>
       </c>
@@ -5044,7 +5220,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="57" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A57">
         <v>56</v>
       </c>
@@ -5064,7 +5240,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="58" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A58">
         <v>57</v>
       </c>
@@ -5084,7 +5260,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="59" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A59">
         <v>58</v>
       </c>
@@ -5104,7 +5280,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="60" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A60">
         <v>59</v>
       </c>
@@ -5124,7 +5300,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="61" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A61">
         <v>60</v>
       </c>
@@ -5144,7 +5320,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="62" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A62">
         <v>61</v>
       </c>
@@ -5196,7 +5372,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="64" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A64">
         <v>63</v>
       </c>
@@ -5216,7 +5392,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="65" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A65">
         <v>64</v>
       </c>
@@ -5236,7 +5412,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="66" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A66">
         <v>65</v>
       </c>
@@ -5256,7 +5432,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="67" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A67">
         <v>66</v>
       </c>
@@ -5276,7 +5452,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="68" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A68">
         <v>67</v>
       </c>
@@ -5296,7 +5472,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="69" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A69">
         <v>68</v>
       </c>
@@ -5316,7 +5492,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="70" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A70">
         <v>69</v>
       </c>
@@ -5336,7 +5512,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="71" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A71">
         <v>70</v>
       </c>
@@ -5356,7 +5532,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="72" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A72">
         <v>71</v>
       </c>
@@ -5376,7 +5552,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="73" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A73">
         <v>72</v>
       </c>
@@ -5396,7 +5572,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="74" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A74">
         <v>73</v>
       </c>
@@ -6202,7 +6378,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="108" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A108">
         <v>178</v>
       </c>
@@ -6237,7 +6413,7 @@
         <v>420</v>
       </c>
     </row>
-    <row r="109" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A109">
         <v>110</v>
       </c>
@@ -6269,7 +6445,7 @@
         <v>420</v>
       </c>
     </row>
-    <row r="110" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A110">
         <v>156</v>
       </c>
@@ -6301,7 +6477,7 @@
         <v>420</v>
       </c>
     </row>
-    <row r="111" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A111">
         <v>123</v>
       </c>
@@ -6333,7 +6509,7 @@
         <v>420</v>
       </c>
     </row>
-    <row r="112" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A112">
         <v>122</v>
       </c>
@@ -6365,7 +6541,7 @@
         <v>420</v>
       </c>
     </row>
-    <row r="113" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A113">
         <v>107</v>
       </c>
@@ -6403,7 +6579,7 @@
         <v>420</v>
       </c>
     </row>
-    <row r="114" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A114">
         <v>148</v>
       </c>
@@ -6435,7 +6611,7 @@
         <v>420</v>
       </c>
     </row>
-    <row r="115" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A115">
         <v>133</v>
       </c>
@@ -6470,7 +6646,7 @@
         <v>420</v>
       </c>
     </row>
-    <row r="116" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A116">
         <v>170</v>
       </c>
@@ -6508,7 +6684,7 @@
         <v>420</v>
       </c>
     </row>
-    <row r="117" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A117">
         <v>138</v>
       </c>
@@ -6540,7 +6716,7 @@
         <v>420</v>
       </c>
     </row>
-    <row r="118" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A118">
         <v>150</v>
       </c>
@@ -6578,7 +6754,7 @@
         <v>420</v>
       </c>
     </row>
-    <row r="119" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A119">
         <v>155</v>
       </c>
@@ -6610,7 +6786,7 @@
         <v>420</v>
       </c>
     </row>
-    <row r="120" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A120">
         <v>166</v>
       </c>
@@ -6645,7 +6821,7 @@
         <v>420</v>
       </c>
     </row>
-    <row r="121" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A121">
         <v>142</v>
       </c>
@@ -6677,7 +6853,7 @@
         <v>420</v>
       </c>
     </row>
-    <row r="122" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A122">
         <v>128</v>
       </c>
@@ -6715,7 +6891,7 @@
         <v>420</v>
       </c>
     </row>
-    <row r="123" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A123">
         <v>154</v>
       </c>
@@ -6747,7 +6923,7 @@
         <v>420</v>
       </c>
     </row>
-    <row r="124" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A124">
         <v>179</v>
       </c>
@@ -6785,7 +6961,7 @@
         <v>420</v>
       </c>
     </row>
-    <row r="125" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A125">
         <v>129</v>
       </c>
@@ -6820,7 +6996,7 @@
         <v>420</v>
       </c>
     </row>
-    <row r="126" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A126">
         <v>113</v>
       </c>
@@ -6849,7 +7025,7 @@
         <v>420</v>
       </c>
     </row>
-    <row r="127" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A127">
         <v>159</v>
       </c>
@@ -6878,7 +7054,7 @@
         <v>420</v>
       </c>
     </row>
-    <row r="128" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A128">
         <v>108</v>
       </c>
@@ -6901,7 +7077,7 @@
         <v>420</v>
       </c>
     </row>
-    <row r="129" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A129">
         <v>109</v>
       </c>
@@ -6930,7 +7106,7 @@
         <v>420</v>
       </c>
     </row>
-    <row r="130" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A130">
         <v>111</v>
       </c>
@@ -6959,7 +7135,7 @@
         <v>420</v>
       </c>
     </row>
-    <row r="131" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A131">
         <v>112</v>
       </c>
@@ -6991,7 +7167,7 @@
         <v>420</v>
       </c>
     </row>
-    <row r="132" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A132">
         <v>114</v>
       </c>
@@ -7017,7 +7193,7 @@
         <v>420</v>
       </c>
     </row>
-    <row r="133" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A133">
         <v>115</v>
       </c>
@@ -7040,7 +7216,7 @@
         <v>420</v>
       </c>
     </row>
-    <row r="134" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A134">
         <v>116</v>
       </c>
@@ -7072,7 +7248,7 @@
         <v>420</v>
       </c>
     </row>
-    <row r="135" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A135">
         <v>117</v>
       </c>
@@ -7095,7 +7271,7 @@
         <v>420</v>
       </c>
     </row>
-    <row r="136" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A136">
         <v>118</v>
       </c>
@@ -7124,7 +7300,7 @@
         <v>420</v>
       </c>
     </row>
-    <row r="137" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A137">
         <v>119</v>
       </c>
@@ -7147,7 +7323,7 @@
         <v>420</v>
       </c>
     </row>
-    <row r="138" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A138">
         <v>120</v>
       </c>
@@ -7176,7 +7352,7 @@
         <v>420</v>
       </c>
     </row>
-    <row r="139" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A139">
         <v>121</v>
       </c>
@@ -7199,7 +7375,7 @@
         <v>420</v>
       </c>
     </row>
-    <row r="140" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A140">
         <v>124</v>
       </c>
@@ -7222,7 +7398,7 @@
         <v>420</v>
       </c>
     </row>
-    <row r="141" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A141">
         <v>125</v>
       </c>
@@ -7251,7 +7427,7 @@
         <v>420</v>
       </c>
     </row>
-    <row r="142" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A142">
         <v>126</v>
       </c>
@@ -7280,7 +7456,7 @@
         <v>420</v>
       </c>
     </row>
-    <row r="143" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A143">
         <v>127</v>
       </c>
@@ -7306,7 +7482,7 @@
         <v>420</v>
       </c>
     </row>
-    <row r="144" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A144">
         <v>130</v>
       </c>
@@ -7335,7 +7511,7 @@
         <v>420</v>
       </c>
     </row>
-    <row r="145" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A145">
         <v>131</v>
       </c>
@@ -7364,7 +7540,7 @@
         <v>420</v>
       </c>
     </row>
-    <row r="146" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A146">
         <v>132</v>
       </c>
@@ -7393,7 +7569,7 @@
         <v>420</v>
       </c>
     </row>
-    <row r="147" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A147">
         <v>134</v>
       </c>
@@ -7416,7 +7592,7 @@
         <v>420</v>
       </c>
     </row>
-    <row r="148" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A148">
         <v>135</v>
       </c>
@@ -7439,7 +7615,7 @@
         <v>420</v>
       </c>
     </row>
-    <row r="149" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A149">
         <v>136</v>
       </c>
@@ -7462,7 +7638,7 @@
         <v>420</v>
       </c>
     </row>
-    <row r="150" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A150">
         <v>137</v>
       </c>
@@ -7494,7 +7670,7 @@
         <v>420</v>
       </c>
     </row>
-    <row r="151" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A151">
         <v>139</v>
       </c>
@@ -7526,7 +7702,7 @@
         <v>420</v>
       </c>
     </row>
-    <row r="152" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A152">
         <v>140</v>
       </c>
@@ -7552,7 +7728,7 @@
         <v>420</v>
       </c>
     </row>
-    <row r="153" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A153">
         <v>141</v>
       </c>
@@ -7584,7 +7760,7 @@
         <v>420</v>
       </c>
     </row>
-    <row r="154" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A154">
         <v>143</v>
       </c>
@@ -7610,7 +7786,7 @@
         <v>420</v>
       </c>
     </row>
-    <row r="155" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A155">
         <v>144</v>
       </c>
@@ -7636,7 +7812,7 @@
         <v>420</v>
       </c>
     </row>
-    <row r="156" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A156">
         <v>145</v>
       </c>
@@ -7665,7 +7841,7 @@
         <v>420</v>
       </c>
     </row>
-    <row r="157" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A157">
         <v>146</v>
       </c>
@@ -7691,7 +7867,7 @@
         <v>420</v>
       </c>
     </row>
-    <row r="158" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A158">
         <v>147</v>
       </c>
@@ -7720,7 +7896,7 @@
         <v>420</v>
       </c>
     </row>
-    <row r="159" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A159">
         <v>149</v>
       </c>
@@ -7749,7 +7925,7 @@
         <v>420</v>
       </c>
     </row>
-    <row r="160" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A160">
         <v>151</v>
       </c>
@@ -7778,7 +7954,7 @@
         <v>420</v>
       </c>
     </row>
-    <row r="161" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A161">
         <v>152</v>
       </c>
@@ -7807,7 +7983,7 @@
         <v>420</v>
       </c>
     </row>
-    <row r="162" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A162">
         <v>153</v>
       </c>
@@ -7830,7 +8006,7 @@
         <v>420</v>
       </c>
     </row>
-    <row r="163" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A163">
         <v>157</v>
       </c>
@@ -7853,7 +8029,7 @@
         <v>420</v>
       </c>
     </row>
-    <row r="164" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A164">
         <v>158</v>
       </c>
@@ -7876,7 +8052,7 @@
         <v>420</v>
       </c>
     </row>
-    <row r="165" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A165">
         <v>160</v>
       </c>
@@ -7899,7 +8075,7 @@
         <v>420</v>
       </c>
     </row>
-    <row r="166" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A166">
         <v>161</v>
       </c>
@@ -7922,7 +8098,7 @@
         <v>420</v>
       </c>
     </row>
-    <row r="167" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A167">
         <v>162</v>
       </c>
@@ -7945,7 +8121,7 @@
         <v>420</v>
       </c>
     </row>
-    <row r="168" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A168">
         <v>163</v>
       </c>
@@ -7968,7 +8144,7 @@
         <v>420</v>
       </c>
     </row>
-    <row r="169" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A169">
         <v>164</v>
       </c>
@@ -7991,7 +8167,7 @@
         <v>420</v>
       </c>
     </row>
-    <row r="170" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A170">
         <v>165</v>
       </c>
@@ -8014,7 +8190,7 @@
         <v>420</v>
       </c>
     </row>
-    <row r="171" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A171">
         <v>167</v>
       </c>
@@ -8037,7 +8213,7 @@
         <v>420</v>
       </c>
     </row>
-    <row r="172" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A172">
         <v>168</v>
       </c>
@@ -8060,7 +8236,7 @@
         <v>420</v>
       </c>
     </row>
-    <row r="173" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A173">
         <v>169</v>
       </c>
@@ -8086,7 +8262,7 @@
         <v>420</v>
       </c>
     </row>
-    <row r="174" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A174">
         <v>171</v>
       </c>
@@ -8115,7 +8291,7 @@
         <v>420</v>
       </c>
     </row>
-    <row r="175" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A175">
         <v>172</v>
       </c>
@@ -8138,7 +8314,7 @@
         <v>420</v>
       </c>
     </row>
-    <row r="176" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A176">
         <v>173</v>
       </c>
@@ -8167,7 +8343,7 @@
         <v>420</v>
       </c>
     </row>
-    <row r="177" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A177">
         <v>174</v>
       </c>
@@ -8196,7 +8372,7 @@
         <v>420</v>
       </c>
     </row>
-    <row r="178" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A178">
         <v>175</v>
       </c>
@@ -8219,7 +8395,7 @@
         <v>420</v>
       </c>
     </row>
-    <row r="179" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A179">
         <v>176</v>
       </c>
@@ -8242,7 +8418,7 @@
         <v>420</v>
       </c>
     </row>
-    <row r="180" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A180">
         <v>177</v>
       </c>
@@ -8274,7 +8450,7 @@
         <v>420</v>
       </c>
     </row>
-    <row r="181" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A181">
         <v>180</v>
       </c>
@@ -8297,7 +8473,7 @@
         <v>420</v>
       </c>
     </row>
-    <row r="182" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A182">
         <v>181</v>
       </c>
@@ -8320,7 +8496,7 @@
         <v>420</v>
       </c>
     </row>
-    <row r="183" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A183">
         <v>182</v>
       </c>
@@ -8343,7 +8519,7 @@
         <v>420</v>
       </c>
     </row>
-    <row r="184" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A184">
         <v>189</v>
       </c>
@@ -8378,7 +8554,7 @@
         <v>853</v>
       </c>
     </row>
-    <row r="185" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A185">
         <v>209</v>
       </c>
@@ -8413,7 +8589,7 @@
         <v>853</v>
       </c>
     </row>
-    <row r="186" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A186">
         <v>216</v>
       </c>
@@ -8448,7 +8624,7 @@
         <v>853</v>
       </c>
     </row>
-    <row r="187" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A187">
         <v>219</v>
       </c>
@@ -8483,7 +8659,7 @@
         <v>853</v>
       </c>
     </row>
-    <row r="188" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="188" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A188">
         <v>205</v>
       </c>
@@ -8518,7 +8694,7 @@
         <v>853</v>
       </c>
     </row>
-    <row r="189" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="189" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A189">
         <v>203</v>
       </c>
@@ -8550,7 +8726,7 @@
         <v>853</v>
       </c>
     </row>
-    <row r="190" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="190" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A190">
         <v>211</v>
       </c>
@@ -8588,7 +8764,7 @@
         <v>853</v>
       </c>
     </row>
-    <row r="191" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="191" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A191">
         <v>213</v>
       </c>
@@ -8626,7 +8802,7 @@
         <v>853</v>
       </c>
     </row>
-    <row r="192" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="192" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A192">
         <v>217</v>
       </c>
@@ -8664,7 +8840,7 @@
         <v>853</v>
       </c>
     </row>
-    <row r="193" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="193" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A193">
         <v>208</v>
       </c>
@@ -8693,7 +8869,7 @@
         <v>853</v>
       </c>
     </row>
-    <row r="194" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="194" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A194">
         <v>202</v>
       </c>
@@ -8731,7 +8907,7 @@
         <v>853</v>
       </c>
     </row>
-    <row r="195" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="195" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A195">
         <v>190</v>
       </c>
@@ -8766,7 +8942,7 @@
         <v>853</v>
       </c>
     </row>
-    <row r="196" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="196" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A196">
         <v>194</v>
       </c>
@@ -8804,7 +8980,7 @@
         <v>853</v>
       </c>
     </row>
-    <row r="197" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="197" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A197">
         <v>195</v>
       </c>
@@ -8836,7 +9012,7 @@
         <v>853</v>
       </c>
     </row>
-    <row r="198" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="198" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A198">
         <v>192</v>
       </c>
@@ -8874,7 +9050,7 @@
         <v>853</v>
       </c>
     </row>
-    <row r="199" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="199" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A199">
         <v>215</v>
       </c>
@@ -8912,7 +9088,7 @@
         <v>853</v>
       </c>
     </row>
-    <row r="200" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="200" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A200">
         <v>214</v>
       </c>
@@ -8944,7 +9120,7 @@
         <v>853</v>
       </c>
     </row>
-    <row r="201" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="201" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A201">
         <v>201</v>
       </c>
@@ -8982,7 +9158,7 @@
         <v>853</v>
       </c>
     </row>
-    <row r="202" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="202" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A202">
         <v>183</v>
       </c>
@@ -9020,7 +9196,7 @@
         <v>853</v>
       </c>
     </row>
-    <row r="203" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="203" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A203">
         <v>207</v>
       </c>
@@ -9058,7 +9234,7 @@
         <v>853</v>
       </c>
     </row>
-    <row r="204" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="204" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A204">
         <v>200</v>
       </c>
@@ -9090,7 +9266,7 @@
         <v>853</v>
       </c>
     </row>
-    <row r="205" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="205" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A205">
         <v>199</v>
       </c>
@@ -9128,7 +9304,7 @@
         <v>853</v>
       </c>
     </row>
-    <row r="206" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="206" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A206">
         <v>212</v>
       </c>
@@ -9160,7 +9336,7 @@
         <v>853</v>
       </c>
     </row>
-    <row r="207" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="207" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A207">
         <v>191</v>
       </c>
@@ -9195,7 +9371,7 @@
         <v>853</v>
       </c>
     </row>
-    <row r="208" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="208" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A208">
         <v>204</v>
       </c>
@@ -9227,7 +9403,7 @@
         <v>853</v>
       </c>
     </row>
-    <row r="209" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="209" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A209">
         <v>188</v>
       </c>
@@ -9265,7 +9441,7 @@
         <v>853</v>
       </c>
     </row>
-    <row r="210" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="210" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A210">
         <v>185</v>
       </c>
@@ -9303,7 +9479,7 @@
         <v>853</v>
       </c>
     </row>
-    <row r="211" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="211" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A211">
         <v>186</v>
       </c>
@@ -9335,7 +9511,7 @@
         <v>853</v>
       </c>
     </row>
-    <row r="212" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="212" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A212">
         <v>184</v>
       </c>
@@ -9370,7 +9546,7 @@
         <v>853</v>
       </c>
     </row>
-    <row r="213" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="213" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A213">
         <v>187</v>
       </c>
@@ -9399,7 +9575,7 @@
         <v>853</v>
       </c>
     </row>
-    <row r="214" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="214" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A214">
         <v>193</v>
       </c>
@@ -9431,7 +9607,7 @@
         <v>853</v>
       </c>
     </row>
-    <row r="215" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="215" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A215">
         <v>196</v>
       </c>
@@ -9463,7 +9639,7 @@
         <v>853</v>
       </c>
     </row>
-    <row r="216" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="216" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A216">
         <v>197</v>
       </c>
@@ -9495,7 +9671,7 @@
         <v>853</v>
       </c>
     </row>
-    <row r="217" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="217" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A217">
         <v>198</v>
       </c>
@@ -9521,7 +9697,7 @@
         <v>853</v>
       </c>
     </row>
-    <row r="218" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="218" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A218">
         <v>206</v>
       </c>
@@ -9550,7 +9726,7 @@
         <v>853</v>
       </c>
     </row>
-    <row r="219" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="219" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A219">
         <v>210</v>
       </c>
@@ -9582,7 +9758,7 @@
         <v>853</v>
       </c>
     </row>
-    <row r="220" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="220" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A220">
         <v>218</v>
       </c>
